--- a/artfynd/A 37295-2026 artfynd.xlsx
+++ b/artfynd/A 37295-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135975496</v>
       </c>
       <c r="B2" t="n">
-        <v>98276</v>
+        <v>98277</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>135975508</v>
       </c>
       <c r="B3" t="n">
-        <v>98276</v>
+        <v>98277</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>135975550</v>
       </c>
       <c r="B4" t="n">
-        <v>98276</v>
+        <v>98277</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>135975617</v>
       </c>
       <c r="B9" t="n">
-        <v>106467</v>
+        <v>106468</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>135975845</v>
       </c>
       <c r="B11" t="n">
-        <v>98209</v>
+        <v>98210</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2104,7 +2104,7 @@
         <v>135975623</v>
       </c>
       <c r="B15" t="n">
-        <v>98203</v>
+        <v>98204</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2211,7 +2211,7 @@
         <v>135975749</v>
       </c>
       <c r="B16" t="n">
-        <v>98203</v>
+        <v>98204</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2318,7 +2318,7 @@
         <v>135975605</v>
       </c>
       <c r="B17" t="n">
-        <v>98392</v>
+        <v>98393</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
